--- a/result/organelle_protein_abundance_ecGEMs_rosemary.xlsx
+++ b/result/organelle_protein_abundance_ecGEMs_rosemary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/result/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB4D223-2C3E-7A45-8305-166B93C8DDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D100111-B3EF-364D-9FA0-4BD7C6A8F45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30920" yWindow="940" windowWidth="38180" windowHeight="21200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="500" windowWidth="25780" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -610,1680 +610,6 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="406542304"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-SE"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-SE"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>mitochondrion</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.35</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$C$2:$C$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>1.554505329837952E-3</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.4607445812660929E-3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.389921121527817E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.132055144528843E-3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.1683725553597311E-3</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.5759503722771291E-3</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.426433783978344E-3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.424243781485717E-3</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.6281626411098369E-3</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.4787270748123429E-3</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.394776382373676E-3</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.3956518492364599E-3</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.0916816170607339E-3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.9447982209754289E-3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2.1303493039246221E-3</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2.3370506952047039E-3</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2.486697357324459E-3</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2.4830247432920372E-3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5553-FD44-8C87-DC8F706A17E4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="423951216"/>
-        <c:axId val="435885984"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="423951216"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-SE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="435885984"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="435885984"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-SE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="423951216"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-SE"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-SE"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>fungal-type vacuole</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.35</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$F$2:$F$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>1.4090210871919601E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.2290915102561699E-4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.2907891924807E-4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.1203841204425007E-5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>9.0774160083834991E-5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.1713614964927301E-4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>8.7161569886248002E-5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8.6603820704934009E-5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.06308355953004E-4</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>8.6563128440230976E-5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>8.293966947341201E-5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>8.3278629341560986E-5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.6885155325144799E-4</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.6594029169646901E-4</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.62577172017433E-4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2.4440169136199998E-4</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2.5456289613657289E-4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2.5277248932035801E-4</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-9DC9-5142-BD51-4D3595B68856}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="423587984"/>
-        <c:axId val="432582688"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="423587984"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-SE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="432582688"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="432582688"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-SE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="423587984"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-SE"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-SE"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$G$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>lipid droplet</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.35</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$G$2:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>2.3042462106297599E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.5470624977366099E-4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.8217738988667099E-4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.25710381312225E-4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.17126269562505E-4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3.3170229699201802E-4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.9449342528016599E-4</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.0787930207661999E-4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2.4783026677049598E-4</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.6052996734698701E-4</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.6475352165362011E-4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.85381544645871E-4</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>3.1613481232766112E-4</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>3.10803987485948E-4</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>3.2821944206927998E-4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>4.1777680497685798E-4</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>5.5002046976141707E-4</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>4.4708518517989898E-4</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3AFC-6F47-A162-8E597EAC1831}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="425244464"/>
-        <c:axId val="424974592"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="425244464"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-SE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="424974592"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="424974592"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-SE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="425244464"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-SE"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-SE"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$H$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>endoplasmic reticulum</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.12771194225721785"/>
-                  <c:y val="-3.4617235345581802E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-SE"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.35</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$H$2:$H$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>4.7028046203040991E-5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4.3855254919024989E-5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4.2066315448446993E-5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.6124792705032998E-5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.0709281787896998E-5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.5145592713796997E-5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>5.4126547565832001E-5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>5.4233554032421009E-5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>6.267239897635701E-5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>5.9326428772213021E-5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5.9706825725491997E-5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.4899491643306013E-5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>7.3079951329090993E-5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>7.535358593703497E-5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>7.627272152385499E-5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>7.9527739579512947E-5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>8.2850852699815021E-5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>8.5853086015949998E-5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-31C3-3B49-8FC0-7FA74C56C32D}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="416035568"/>
-        <c:axId val="415765440"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="416035568"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-SE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="415765440"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="415765440"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-SE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="416035568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4988,11 +3314,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$1</c:f>
+              <c:f>Sheet1!$L$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>cytosol</c:v>
+                  <c:v>mitochondrial outer membrane</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5019,6 +3345,56 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.18876636987502057"/>
+                  <c:y val="-6.9022952457528083E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-SE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet1!$B$2:$B$19</c:f>
@@ -5084,63 +3460,63 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$19</c:f>
+              <c:f>Sheet1!$L$2:$L$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>8.2714289338473685E-4</c:v>
+                  <c:v>2.2784888578910001E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.4192730068679109E-4</c:v>
+                  <c:v>2.1097816572080002E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.02731298572263E-4</c:v>
+                  <c:v>2.081565595782E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.936492824849146E-4</c:v>
+                  <c:v>1.4552376207140001E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.9706349486606186E-4</c:v>
+                  <c:v>1.6410701073040001E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.1460272223714285E-4</c:v>
+                  <c:v>2.143427051508E-5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.3554086263570237E-4</c:v>
+                  <c:v>2.0999704918510001E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.7226301219132101E-4</c:v>
+                  <c:v>2.0161018269240002E-5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.6454398395773414E-4</c:v>
+                  <c:v>2.444534715658E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.202914127668788E-4</c:v>
+                  <c:v>2.2140828376559999E-5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.5353867565239715E-4</c:v>
+                  <c:v>2.2147184484E-5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6.9335569790823803E-4</c:v>
+                  <c:v>2.1781517448910001E-5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.1311536148076811E-3</c:v>
+                  <c:v>2.814804764795E-5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.074373258554613E-3</c:v>
+                  <c:v>2.4954111145119999E-5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.144495394398213E-3</c:v>
+                  <c:v>2.9122359539919999E-5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.3858683227853401E-3</c:v>
+                  <c:v>2.874702908759E-5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.534481125751709E-3</c:v>
+                  <c:v>2.727377272881E-5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.426624510038333E-3</c:v>
+                  <c:v>3.1379029052549997E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5148,7 +3524,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0001-9044-B22B-C77836A158F0}"/>
+              <c16:uniqueId val="{00000000-0A65-4C48-804B-AA22A544433F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5160,11 +3536,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="427841840"/>
-        <c:axId val="415312480"/>
+        <c:axId val="435435968"/>
+        <c:axId val="435192976"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="427841840"/>
+        <c:axId val="435435968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5221,12 +3597,12 @@
             <a:endParaRPr lang="en-SE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="415312480"/>
+        <c:crossAx val="435192976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="415312480"/>
+        <c:axId val="435192976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5283,413 +3659,7 @@
             <a:endParaRPr lang="en-SE"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427841840"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-SE"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-SE"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>nucleus</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Sheet1!$B$2:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.05</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.13</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.18</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.35</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Sheet1!$E$2:$E$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>6.809576837215202E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.6991755099894592E-4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6.0417388454623601E-4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.4701462518113697E-4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.5879830448923179E-4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6.5937744821812001E-4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6.4886387835566702E-4</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>6.7776987861080775E-4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7.413553883853359E-4</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>6.729246035505318E-4</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5.9963631580107677E-4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>6.2986832778032719E-4</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9.4721595987320019E-4</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>8.9355163156645118E-4</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>9.5523407550609216E-4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1.092349573714423E-3</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1.1770513071970481E-3</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1.0911683435436089E-3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-90C0-6344-9B3D-752DDE140ACA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="430660736"/>
-        <c:axId val="430884480"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="430660736"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-SE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="430884480"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="430884480"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-SE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="430660736"/>
+        <c:crossAx val="435435968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5746,166 +3716,6 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors10.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6225,46 +4035,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -6781,7 +4551,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7297,7 +5067,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7813,7 +5583,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8329,7 +6099,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8845,7 +6615,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -9361,7 +7131,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -9877,2587 +7647,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -13193,14 +8383,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>781050</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1086492</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>590549</xdr:colOff>
       <xdr:row>72</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
@@ -13229,23 +8419,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>880960</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>27007</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>393700</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>610885</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>176836</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="27" name="Chart 26">
+        <xdr:cNvPr id="34" name="Chart 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49011ED4-EA26-5B37-44C9-45DEBDB738FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDD31AE0-AA1F-9202-967C-5D1FFD86563C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13258,186 +8448,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>393700</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="28" name="Chart 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6D3A93C-4C8F-EE51-868F-9ECB2D091526}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>406400</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="30" name="Chart 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA7C6A3A-46E4-0AF0-A92A-3AEF2D6EA945}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>406400</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="31" name="Chart 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{535D6BDA-0BFA-2742-9634-91B85D28A2D3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>736600</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="32" name="Chart 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8D52A3F-4227-9BB4-C2A2-95751AA811B7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>698500</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="33" name="Chart 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5787B3A4-F99B-1932-5610-9D8C2FB1C67E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -14932,6 +9942,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/result/organelle_protein_abundance_ecGEMs_rosemary.xlsx
+++ b/result/organelle_protein_abundance_ecGEMs_rosemary.xlsx
@@ -538,7 +538,7 @@
         <v>0.0008271428933847369</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0006809576837215202</v>
+        <v>0.0006809576837215199</v>
       </c>
       <c r="E2" t="n">
         <v>0.000140902108719196</v>
@@ -547,7 +547,7 @@
         <v>0.000230424621062976</v>
       </c>
       <c r="G2" t="n">
-        <v>4.702804620304099e-05</v>
+        <v>4.702804620304102e-05</v>
       </c>
       <c r="H2" t="n">
         <v>3.721176535657498e-05</v>
@@ -559,10 +559,10 @@
         <v>1.9107333851922e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.278488857891e-05</v>
+        <v>2.278488857891001e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>8.153574401448999e-06</v>
+        <v>8.153574401449e-06</v>
       </c>
       <c r="M2" t="n">
         <v>4.807132404725e-06</v>
@@ -601,10 +601,10 @@
         <v>0.001460744581266093</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007419273006867911</v>
+        <v>0.0007419273006867909</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006699175509989459</v>
+        <v>0.0006699175509989457</v>
       </c>
       <c r="E3" t="n">
         <v>0.000122909151025617</v>
@@ -613,13 +613,13 @@
         <v>0.000154706249773661</v>
       </c>
       <c r="G3" t="n">
-        <v>4.385525491902499e-05</v>
+        <v>4.3855254919025e-05</v>
       </c>
       <c r="H3" t="n">
         <v>3.5622229652718e-05</v>
       </c>
       <c r="I3" t="n">
-        <v>9.873062316118202e-05</v>
+        <v>9.8730623161182e-05</v>
       </c>
       <c r="J3" t="n">
         <v>1.7918686272561e-05</v>
@@ -628,7 +628,7 @@
         <v>2.109781657208e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>7.54942784943e-06</v>
+        <v>7.549427849429999e-06</v>
       </c>
       <c r="M3" t="n">
         <v>4.10400489123e-06</v>
@@ -667,10 +667,10 @@
         <v>0.001389921121527817</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000702731298572263</v>
+        <v>0.0007027312985722629</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000604173884546236</v>
+        <v>0.0006041738845462363</v>
       </c>
       <c r="E4" t="n">
         <v>0.00012907891924807</v>
@@ -679,13 +679,13 @@
         <v>0.000182177389886671</v>
       </c>
       <c r="G4" t="n">
-        <v>4.206631544844699e-05</v>
+        <v>4.206631544844701e-05</v>
       </c>
       <c r="H4" t="n">
         <v>3.1721285806796e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>9.440182293646301e-05</v>
+        <v>9.4401822936463e-05</v>
       </c>
       <c r="J4" t="n">
         <v>1.7512137935244e-05</v>
@@ -694,13 +694,13 @@
         <v>2.081565595782e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>7.557336071243e-06</v>
+        <v>7.557336071243001e-06</v>
       </c>
       <c r="M4" t="n">
         <v>4.091763683615e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>6.09807433796e-07</v>
+        <v>6.098074337959999e-07</v>
       </c>
       <c r="O4" t="n">
         <v>1.69666332621e-07</v>
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001132055144528843</v>
+        <v>0.001132055144528844</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0005936492824849146</v>
+        <v>0.0005936492824849148</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000547014625181137</v>
+        <v>0.0005470146251811371</v>
       </c>
       <c r="E5" t="n">
-        <v>8.120384120442501e-05</v>
+        <v>8.120384120442498e-05</v>
       </c>
       <c r="F5" t="n">
         <v>0.000125710381312225</v>
@@ -760,7 +760,7 @@
         <v>1.455237620714e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>6.427842627878001e-06</v>
+        <v>6.427842627878e-06</v>
       </c>
       <c r="M5" t="n">
         <v>4.418022398885e-06</v>
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001168372555359731</v>
+        <v>0.001168372555359732</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005970634948660619</v>
+        <v>0.000597063494866062</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0005587983044892318</v>
+        <v>0.0005587983044892321</v>
       </c>
       <c r="E6" t="n">
-        <v>9.077416008383499e-05</v>
+        <v>9.0774160083835e-05</v>
       </c>
       <c r="F6" t="n">
         <v>0.000117126269562505</v>
@@ -826,13 +826,13 @@
         <v>1.641070107304e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>6.642580152757001e-06</v>
+        <v>6.642580152756999e-06</v>
       </c>
       <c r="M6" t="n">
         <v>4.572713602386e-06</v>
       </c>
       <c r="N6" t="n">
-        <v>5.721140868590001e-07</v>
+        <v>5.72114086859e-07</v>
       </c>
       <c r="O6" t="n">
         <v>1.49075581693e-07</v>
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001575950372277129</v>
+        <v>0.001575950372277131</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009146027222371428</v>
+        <v>0.0009146027222371431</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00065937744821812</v>
+        <v>0.0006593774482181199</v>
       </c>
       <c r="E7" t="n">
         <v>0.000117136149649273</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000331702296992018</v>
+        <v>0.0003317022969920181</v>
       </c>
       <c r="G7" t="n">
         <v>4.5145592713797e-05</v>
@@ -895,10 +895,10 @@
         <v>9.605556304322e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>5.450156439617999e-06</v>
+        <v>5.450156439618e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>5.87657569629e-07</v>
+        <v>5.876575696289999e-07</v>
       </c>
       <c r="O7" t="n">
         <v>1.06245612254e-07</v>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001426433783978344</v>
+        <v>0.001426433783978345</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0007355408626357024</v>
+        <v>0.0007355408626357019</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000648863878355667</v>
+        <v>0.0006488638783556673</v>
       </c>
       <c r="E8" t="n">
         <v>8.7161569886248e-05</v>
@@ -943,7 +943,7 @@
         <v>0.000194493425280166</v>
       </c>
       <c r="G8" t="n">
-        <v>5.4126547565832e-05</v>
+        <v>5.412654756583202e-05</v>
       </c>
       <c r="H8" t="n">
         <v>5.188366716982499e-05</v>
@@ -961,10 +961,10 @@
         <v>9.138060582981001e-06</v>
       </c>
       <c r="M8" t="n">
-        <v>5.828014403199e-06</v>
+        <v>5.828014403199001e-06</v>
       </c>
       <c r="N8" t="n">
-        <v>7.78252690495e-07</v>
+        <v>7.782526904950001e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.63665956998e-07</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001424243781485717</v>
+        <v>0.001424243781485716</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000772263012191321</v>
+        <v>0.0007722630121913211</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0006777698786108077</v>
+        <v>0.0006777698786108076</v>
       </c>
       <c r="E9" t="n">
         <v>8.660382070493401e-05</v>
@@ -1009,13 +1009,13 @@
         <v>0.00020787930207662</v>
       </c>
       <c r="G9" t="n">
-        <v>5.423355403242101e-05</v>
+        <v>5.423355403242103e-05</v>
       </c>
       <c r="H9" t="n">
         <v>4.9459221464865e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001419080703416919</v>
+        <v>0.000141908070341692</v>
       </c>
       <c r="J9" t="n">
         <v>2.474333099120901e-05</v>
@@ -1024,13 +1024,13 @@
         <v>2.016101826924e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>8.305856010314001e-06</v>
+        <v>8.305856010313999e-06</v>
       </c>
       <c r="M9" t="n">
         <v>5.644894063427e-06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.449025653120002e-07</v>
+        <v>7.449025653120001e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.49354964347e-07</v>
@@ -1063,7 +1063,7 @@
         <v>0.001628162641109837</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0008645439839577341</v>
+        <v>0.000864543983957734</v>
       </c>
       <c r="D10" t="n">
         <v>0.0007413553883853359</v>
@@ -1072,16 +1072,16 @@
         <v>0.000106308355953004</v>
       </c>
       <c r="F10" t="n">
-        <v>0.000247830266770496</v>
+        <v>0.0002478302667704959</v>
       </c>
       <c r="G10" t="n">
-        <v>6.267239897635701e-05</v>
+        <v>6.2672398976357e-05</v>
       </c>
       <c r="H10" t="n">
         <v>5.786227247874898e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001677574470930019</v>
+        <v>0.000167757447093002</v>
       </c>
       <c r="J10" t="n">
         <v>2.889705412265801e-05</v>
@@ -1129,19 +1129,19 @@
         <v>0.001478727074812343</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0007202914127668788</v>
+        <v>0.0007202914127668786</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0006729246035505318</v>
+        <v>0.0006729246035505319</v>
       </c>
       <c r="E11" t="n">
-        <v>8.656312844023098e-05</v>
+        <v>8.656312844023099e-05</v>
       </c>
       <c r="F11" t="n">
         <v>0.000160529967346987</v>
       </c>
       <c r="G11" t="n">
-        <v>5.932642877221302e-05</v>
+        <v>5.9326428772213e-05</v>
       </c>
       <c r="H11" t="n">
         <v>5.550375985464803e-05</v>
@@ -1162,7 +1162,7 @@
         <v>6.014676826820001e-06</v>
       </c>
       <c r="N11" t="n">
-        <v>8.817635708130001e-07</v>
+        <v>8.81763570813e-07</v>
       </c>
       <c r="O11" t="n">
         <v>1.79243159899e-07</v>
@@ -1192,19 +1192,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.001394776382373676</v>
+        <v>0.001394776382373677</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0006535386756523972</v>
+        <v>0.0006535386756523969</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0005996363158010768</v>
+        <v>0.0005996363158010773</v>
       </c>
       <c r="E12" t="n">
         <v>8.293966947341201e-05</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0001647535216536201</v>
+        <v>0.00016475352165362</v>
       </c>
       <c r="G12" t="n">
         <v>5.9706825725492e-05</v>
@@ -1219,7 +1219,7 @@
         <v>2.9419623817777e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2147184484e-05</v>
+        <v>2.214718448400001e-05</v>
       </c>
       <c r="L12" t="n">
         <v>1.0000807346547e-05</v>
@@ -1228,7 +1228,7 @@
         <v>5.887135652105999e-06</v>
       </c>
       <c r="N12" t="n">
-        <v>9.345764390590001e-07</v>
+        <v>9.34576439059e-07</v>
       </c>
       <c r="O12" t="n">
         <v>1.76856388858e-07</v>
@@ -1258,22 +1258,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.00139565184923646</v>
+        <v>0.001395651849236461</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000693355697908238</v>
+        <v>0.0006933556979082377</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0006298683277803272</v>
+        <v>0.0006298683277803271</v>
       </c>
       <c r="E13" t="n">
-        <v>8.327862934156099e-05</v>
+        <v>8.3278629341561e-05</v>
       </c>
       <c r="F13" t="n">
         <v>0.000185381544645871</v>
       </c>
       <c r="G13" t="n">
-        <v>5.489949164330601e-05</v>
+        <v>5.489949164330599e-05</v>
       </c>
       <c r="H13" t="n">
         <v>5.012157435197999e-05</v>
@@ -1294,7 +1294,7 @@
         <v>5.90181297781e-06</v>
       </c>
       <c r="N13" t="n">
-        <v>8.434846144460001e-07</v>
+        <v>8.434846144459998e-07</v>
       </c>
       <c r="O13" t="n">
         <v>1.7953978041e-07</v>
@@ -1324,19 +1324,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.002091681617060734</v>
+        <v>0.002091681617060732</v>
       </c>
       <c r="C14" t="n">
         <v>0.001131153614807681</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0009472159598732002</v>
+        <v>0.0009472159598732</v>
       </c>
       <c r="E14" t="n">
         <v>0.000168851553251448</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0003161348123276611</v>
+        <v>0.000316134812327661</v>
       </c>
       <c r="G14" t="n">
         <v>7.307995132909099e-05</v>
@@ -1357,7 +1357,7 @@
         <v>1.1371804717243e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>7.334028862789999e-06</v>
+        <v>7.334028862790001e-06</v>
       </c>
       <c r="N14" t="n">
         <v>1.273164906155e-06</v>
@@ -1396,7 +1396,7 @@
         <v>0.001074373258554613</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0008935516315664512</v>
+        <v>0.000893551631566451</v>
       </c>
       <c r="E15" t="n">
         <v>0.000165940291696469</v>
@@ -1411,7 +1411,7 @@
         <v>6.565670927224401e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0001928777418990781</v>
+        <v>0.000192877741899078</v>
       </c>
       <c r="J15" t="n">
         <v>3.933027755412599e-05</v>
@@ -1459,10 +1459,10 @@
         <v>0.002130349303924622</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001144495394398213</v>
+        <v>0.001144495394398214</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0009552340755060922</v>
+        <v>0.0009552340755060913</v>
       </c>
       <c r="E16" t="n">
         <v>0.000162577172017433</v>
@@ -1471,7 +1471,7 @@
         <v>0.00032821944206928</v>
       </c>
       <c r="G16" t="n">
-        <v>7.627272152385499e-05</v>
+        <v>7.627272152385504e-05</v>
       </c>
       <c r="H16" t="n">
         <v>6.1505023995093e-05</v>
@@ -1489,7 +1489,7 @@
         <v>1.2655029607194e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>7.070972685420001e-06</v>
+        <v>7.07097268542e-06</v>
       </c>
       <c r="N16" t="n">
         <v>1.325115395667e-06</v>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.002337050695204704</v>
+        <v>0.002337050695204707</v>
       </c>
       <c r="C17" t="n">
-        <v>0.00138586832278534</v>
+        <v>0.001385868322785341</v>
       </c>
       <c r="D17" t="n">
         <v>0.001092349573714423</v>
@@ -1537,7 +1537,7 @@
         <v>0.000417776804976858</v>
       </c>
       <c r="G17" t="n">
-        <v>7.952773957951295e-05</v>
+        <v>7.952773957951301e-05</v>
       </c>
       <c r="H17" t="n">
         <v>6.942122357119901e-05</v>
@@ -1597,10 +1597,10 @@
         <v>0.001177051307197048</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0002545628961365729</v>
+        <v>0.000254562896136573</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0005500204697614171</v>
+        <v>0.000550020469761417</v>
       </c>
       <c r="G18" t="n">
         <v>8.285085269981502e-05</v>
@@ -1615,7 +1615,7 @@
         <v>4.651149162087001e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>2.727377272881e-05</v>
+        <v>2.727377272881001e-05</v>
       </c>
       <c r="L18" t="n">
         <v>1.2001970380439e-05</v>
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.002483024743292037</v>
+        <v>0.002483024743292039</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001426624510038333</v>
+        <v>0.001426624510038332</v>
       </c>
       <c r="D19" t="n">
-        <v>0.001091168343543609</v>
+        <v>0.001091168343543608</v>
       </c>
       <c r="E19" t="n">
         <v>0.000252772489320358</v>
@@ -1669,13 +1669,13 @@
         <v>0.000447085185179899</v>
       </c>
       <c r="G19" t="n">
-        <v>8.585308601595e-05</v>
+        <v>8.585308601595001e-05</v>
       </c>
       <c r="H19" t="n">
         <v>7.492777240859499e-05</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000249970770223323</v>
+        <v>0.0002499707702233231</v>
       </c>
       <c r="J19" t="n">
         <v>4.694084140522601e-05</v>
